--- a/data/form_generation/output/result_MRC1.xlsx
+++ b/data/form_generation/output/result_MRC1.xlsx
@@ -222,7 +222,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -297,6 +297,28 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -312,6 +334,28 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -335,19 +379,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -355,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -368,15 +399,6 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -408,12 +430,6 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -423,73 +439,104 @@
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -866,7 +913,7 @@
     <col width="15.44140625" customWidth="1" min="2" max="2"/>
     <col width="16.109375" customWidth="1" min="3" max="3"/>
     <col width="18.21875" customWidth="1" min="4" max="4"/>
-    <col width="20.33203125" customWidth="1" min="5" max="5"/>
+    <col width="13.109375" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="14"/>
     <col width="16.109375" customWidth="1" min="15" max="15"/>
   </cols>
@@ -886,406 +933,467 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="F4" s="35" t="inlineStr">
+      <c r="F4" s="61" t="n"/>
+      <c r="G4" s="52" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="G4" s="42" t="n"/>
-      <c r="H4" s="42" t="n"/>
-      <c r="I4" s="42" t="n"/>
-      <c r="J4" s="43" t="n"/>
-      <c r="K4" s="31" t="inlineStr">
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="37" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="L4" s="42" t="n"/>
-      <c r="M4" s="42" t="n"/>
-      <c r="N4" s="43" t="n"/>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="L4" s="40" t="n"/>
+      <c r="M4" s="40" t="n"/>
+      <c r="N4" s="44" t="n"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>差分</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>電力会社</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>AA電力</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="F5" s="44" t="n"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>AA工事</t>
         </is>
       </c>
-      <c r="G5" s="42" t="n"/>
-      <c r="H5" s="42" t="n"/>
-      <c r="I5" s="42" t="n"/>
-      <c r="J5" s="43" t="n"/>
-      <c r="K5" s="29" t="inlineStr">
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t>AA工事</t>
         </is>
       </c>
-      <c r="L5" s="42" t="n"/>
-      <c r="M5" s="42" t="n"/>
-      <c r="N5" s="43" t="n"/>
-      <c r="O5" s="11" t="n"/>
+      <c r="L5" s="40" t="n"/>
+      <c r="M5" s="40" t="n"/>
+      <c r="N5" s="44" t="n"/>
+      <c r="O5" s="8" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>工事件名</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>AA工事</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>対象費目1</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="42" t="n"/>
-      <c r="H6" s="42" t="n"/>
-      <c r="I6" s="42" t="n"/>
-      <c r="J6" s="43" t="n"/>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t>施設解体→解体費</t>
-        </is>
-      </c>
-      <c r="L6" s="42" t="n"/>
-      <c r="M6" s="42" t="n"/>
-      <c r="N6" s="43" t="n"/>
-      <c r="O6" s="11" t="n"/>
+      <c r="F6" s="44" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>施設解体一解体費</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="20" t="n"/>
+      <c r="J6" s="20" t="n"/>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>施設解体一解体費</t>
+        </is>
+      </c>
+      <c r="L6" s="40" t="n"/>
+      <c r="M6" s="40" t="n"/>
+      <c r="N6" s="44" t="n"/>
+      <c r="O6" s="8" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>炉型</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>対象費目2</t>
         </is>
       </c>
-      <c r="F7" s="47" t="n"/>
-      <c r="G7" s="42" t="n"/>
-      <c r="H7" s="42" t="n"/>
-      <c r="I7" s="42" t="n"/>
-      <c r="J7" s="43" t="n"/>
-      <c r="K7" s="29" t="inlineStr">
-        <is>
-          <t>処理処分→非該当</t>
-        </is>
-      </c>
-      <c r="L7" s="42" t="n"/>
-      <c r="M7" s="42" t="n"/>
-      <c r="N7" s="43" t="n"/>
-      <c r="O7" s="11" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="48" t="inlineStr">
+        <is>
+          <t>処理処分一非該当</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="n"/>
+      <c r="I7" s="48" t="n"/>
+      <c r="J7" s="48" t="n"/>
+      <c r="K7" s="33" t="inlineStr">
+        <is>
+          <t>処理処分一非該当</t>
+        </is>
+      </c>
+      <c r="L7" s="40" t="n"/>
+      <c r="M7" s="40" t="n"/>
+      <c r="N7" s="44" t="n"/>
+      <c r="O7" s="8" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>計画/実績</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>発電所名</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>AA原子力発電所</t>
         </is>
       </c>
-      <c r="G8" s="42" t="n"/>
-      <c r="H8" s="42" t="n"/>
-      <c r="I8" s="42" t="n"/>
-      <c r="J8" s="43" t="n"/>
-      <c r="K8" s="29" t="inlineStr">
+      <c r="H8" s="46" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="46" t="n"/>
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>AA原子力発電所</t>
         </is>
       </c>
-      <c r="L8" s="42" t="n"/>
-      <c r="M8" s="42" t="n"/>
-      <c r="N8" s="43" t="n"/>
-      <c r="O8" s="11" t="n"/>
+      <c r="L8" s="40" t="n"/>
+      <c r="M8" s="40" t="n"/>
+      <c r="N8" s="44" t="n"/>
+      <c r="O8" s="8" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="E9" s="7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>炉型</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="44" t="n"/>
+      <c r="G9" s="47" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="G9" s="42" t="n"/>
-      <c r="H9" s="42" t="n"/>
-      <c r="I9" s="42" t="n"/>
-      <c r="J9" s="43" t="n"/>
-      <c r="K9" s="33" t="inlineStr">
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="47" t="n"/>
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="L9" s="42" t="n"/>
-      <c r="M9" s="42" t="n"/>
-      <c r="N9" s="43" t="n"/>
-      <c r="O9" s="11" t="n"/>
+      <c r="L9" s="40" t="n"/>
+      <c r="M9" s="40" t="n"/>
+      <c r="N9" s="44" t="n"/>
+      <c r="O9" s="8" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>工期開始日</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="42" t="n"/>
-      <c r="H10" s="42" t="n"/>
-      <c r="I10" s="42" t="n"/>
-      <c r="J10" s="43" t="n"/>
-      <c r="K10" s="33" t="n"/>
-      <c r="L10" s="42" t="n"/>
-      <c r="M10" s="42" t="n"/>
-      <c r="N10" s="43" t="n"/>
-      <c r="O10" s="11" t="n"/>
+      <c r="F10" s="44" t="n"/>
+      <c r="G10" s="47" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="H10" s="47" t="n"/>
+      <c r="I10" s="47" t="n"/>
+      <c r="J10" s="47" t="n"/>
+      <c r="K10" s="29" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="L10" s="40" t="n"/>
+      <c r="M10" s="40" t="n"/>
+      <c r="N10" s="44" t="n"/>
+      <c r="O10" s="8" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>工期終了日</t>
         </is>
       </c>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="42" t="n"/>
-      <c r="H11" s="42" t="n"/>
-      <c r="I11" s="42" t="n"/>
-      <c r="J11" s="43" t="n"/>
-      <c r="K11" s="33" t="n"/>
-      <c r="L11" s="42" t="n"/>
-      <c r="M11" s="42" t="n"/>
-      <c r="N11" s="43" t="n"/>
-      <c r="O11" s="11" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="47" t="inlineStr">
+        <is>
+          <t>2025年9月</t>
+        </is>
+      </c>
+      <c r="H11" s="47" t="n"/>
+      <c r="I11" s="47" t="n"/>
+      <c r="J11" s="47" t="n"/>
+      <c r="K11" s="29" t="inlineStr">
+        <is>
+          <t>2025年9月</t>
+        </is>
+      </c>
+      <c r="L11" s="40" t="n"/>
+      <c r="M11" s="40" t="n"/>
+      <c r="N11" s="44" t="n"/>
+      <c r="O11" s="8" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>全体工期開始日</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="42" t="n"/>
-      <c r="H12" s="42" t="n"/>
-      <c r="I12" s="42" t="n"/>
-      <c r="J12" s="43" t="n"/>
-      <c r="K12" s="33" t="n"/>
-      <c r="L12" s="42" t="n"/>
-      <c r="M12" s="42" t="n"/>
-      <c r="N12" s="43" t="n"/>
-      <c r="O12" s="11" t="n"/>
+      <c r="F12" s="44" t="n"/>
+      <c r="G12" s="47" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="H12" s="47" t="n"/>
+      <c r="I12" s="47" t="n"/>
+      <c r="J12" s="47" t="n"/>
+      <c r="K12" s="29" t="inlineStr">
+        <is>
+          <t>2024年10月</t>
+        </is>
+      </c>
+      <c r="L12" s="40" t="n"/>
+      <c r="M12" s="40" t="n"/>
+      <c r="N12" s="44" t="n"/>
+      <c r="O12" s="8" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>全体工期終了日</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n"/>
-      <c r="I13" s="42" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="33" t="n"/>
-      <c r="L13" s="42" t="n"/>
-      <c r="M13" s="42" t="n"/>
-      <c r="N13" s="43" t="n"/>
-      <c r="O13" s="11" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="47" t="inlineStr">
+        <is>
+          <t>2028年9月</t>
+        </is>
+      </c>
+      <c r="H13" s="47" t="n"/>
+      <c r="I13" s="47" t="n"/>
+      <c r="J13" s="47" t="n"/>
+      <c r="K13" s="29" t="inlineStr">
+        <is>
+          <t>2028年9月</t>
+        </is>
+      </c>
+      <c r="L13" s="40" t="n"/>
+      <c r="M13" s="40" t="n"/>
+      <c r="N13" s="44" t="n"/>
+      <c r="O13" s="8" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>対象号炉1</t>
         </is>
       </c>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="42" t="n"/>
-      <c r="H14" s="42" t="n"/>
-      <c r="I14" s="42" t="n"/>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="29" t="inlineStr">
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="47" t="inlineStr">
         <is>
           <t>AA1号機</t>
         </is>
       </c>
-      <c r="L14" s="42" t="n"/>
-      <c r="M14" s="42" t="n"/>
-      <c r="N14" s="43" t="n"/>
-      <c r="O14" s="11" t="n"/>
+      <c r="H14" s="47" t="n"/>
+      <c r="I14" s="47" t="n"/>
+      <c r="J14" s="47" t="n"/>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>AA1号機</t>
+        </is>
+      </c>
+      <c r="L14" s="40" t="n"/>
+      <c r="M14" s="40" t="n"/>
+      <c r="N14" s="44" t="n"/>
+      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>対象号炉2</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="42" t="n"/>
-      <c r="H15" s="42" t="n"/>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="29" t="inlineStr">
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="47" t="inlineStr">
         <is>
           <t>AA2号機</t>
         </is>
       </c>
-      <c r="L15" s="42" t="n"/>
-      <c r="M15" s="42" t="n"/>
-      <c r="N15" s="43" t="n"/>
-      <c r="O15" s="11" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="47" t="n"/>
+      <c r="J15" s="47" t="n"/>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>AA2号機</t>
+        </is>
+      </c>
+      <c r="L15" s="40" t="n"/>
+      <c r="M15" s="40" t="n"/>
+      <c r="N15" s="44" t="n"/>
+      <c r="O15" s="8" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="49" t="inlineStr">
         <is>
           <t>対象号炉3</t>
         </is>
       </c>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="42" t="n"/>
-      <c r="H16" s="42" t="n"/>
-      <c r="I16" s="42" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="29" t="inlineStr">
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="47" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="L16" s="42" t="n"/>
-      <c r="M16" s="42" t="n"/>
-      <c r="N16" s="43" t="n"/>
-      <c r="O16" s="11" t="n"/>
+      <c r="H16" s="47" t="n"/>
+      <c r="I16" s="47" t="n"/>
+      <c r="J16" s="47" t="n"/>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L16" s="40" t="n"/>
+      <c r="M16" s="40" t="n"/>
+      <c r="N16" s="44" t="n"/>
+      <c r="O16" s="8" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>対象号炉4</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="42" t="n"/>
-      <c r="H17" s="42" t="n"/>
-      <c r="I17" s="42" t="n"/>
-      <c r="J17" s="43" t="n"/>
-      <c r="K17" s="29" t="inlineStr">
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="L17" s="42" t="n"/>
-      <c r="M17" s="42" t="n"/>
-      <c r="N17" s="43" t="n"/>
-      <c r="O17" s="11" t="n"/>
+      <c r="H17" s="47" t="n"/>
+      <c r="I17" s="47" t="n"/>
+      <c r="J17" s="47" t="n"/>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="L17" s="40" t="n"/>
+      <c r="M17" s="40" t="n"/>
+      <c r="N17" s="44" t="n"/>
+      <c r="O17" s="8" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>総額</t>
         </is>
       </c>
-      <c r="F18" s="37" t="inlineStr">
-        <is>
-          <t>40,000円</t>
-        </is>
-      </c>
-      <c r="G18" s="42" t="n"/>
-      <c r="H18" s="42" t="n"/>
-      <c r="I18" s="42" t="n"/>
-      <c r="J18" s="43" t="n"/>
-      <c r="K18" s="29" t="inlineStr">
-        <is>
-          <t>40,000円</t>
-        </is>
-      </c>
-      <c r="L18" s="42" t="n"/>
-      <c r="M18" s="42" t="n"/>
-      <c r="N18" s="43" t="n"/>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="n"/>
+      <c r="I18" s="46" t="n"/>
+      <c r="J18" s="46" t="n"/>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="L18" s="40" t="n"/>
+      <c r="M18" s="40" t="n"/>
+      <c r="N18" s="44" t="n"/>
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>0円</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>全体支払い対象金額</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
-        <is>
-          <t>4,000,000円</t>
-        </is>
-      </c>
-      <c r="G19" s="42" t="n"/>
-      <c r="H19" s="42" t="n"/>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="43" t="n"/>
-      <c r="K19" s="29" t="inlineStr">
-        <is>
-          <t>4,000,000円</t>
-        </is>
-      </c>
-      <c r="L19" s="42" t="n"/>
-      <c r="M19" s="42" t="n"/>
-      <c r="N19" s="43" t="n"/>
-      <c r="O19" s="13" t="inlineStr">
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="L19" s="40" t="n"/>
+      <c r="M19" s="40" t="n"/>
+      <c r="N19" s="44" t="n"/>
+      <c r="O19" s="10" t="inlineStr">
         <is>
           <t>0円</t>
         </is>
@@ -1293,429 +1401,554 @@
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="41" t="n"/>
-      <c r="G20" s="42" t="n"/>
-      <c r="H20" s="42" t="n"/>
-      <c r="I20" s="42" t="n"/>
-      <c r="J20" s="43" t="n"/>
-      <c r="K20" s="41" t="n"/>
-      <c r="L20" s="42" t="n"/>
-      <c r="M20" s="42" t="n"/>
-      <c r="N20" s="43" t="n"/>
-      <c r="O20" s="10" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="39" t="n"/>
+      <c r="L20" s="40" t="n"/>
+      <c r="M20" s="40" t="n"/>
+      <c r="N20" s="44" t="n"/>
+      <c r="O20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="45" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr">
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="45" t="inlineStr">
         <is>
           <t>内容（計画）</t>
         </is>
       </c>
-      <c r="G21" s="42" t="n"/>
-      <c r="H21" s="42" t="n"/>
-      <c r="I21" s="42" t="n"/>
-      <c r="J21" s="43" t="n"/>
-      <c r="K21" s="31" t="inlineStr">
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="40" t="n"/>
+      <c r="J21" s="44" t="n"/>
+      <c r="K21" s="37" t="inlineStr">
         <is>
           <t>内容（実績）</t>
         </is>
       </c>
-      <c r="L21" s="42" t="n"/>
-      <c r="M21" s="42" t="n"/>
-      <c r="N21" s="43" t="n"/>
+      <c r="L21" s="40" t="n"/>
+      <c r="M21" s="40" t="n"/>
+      <c r="N21" s="44" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1">
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="56" t="inlineStr">
         <is>
           <t>実施内容
 ※解体機器や解体物量に関する情報はここには記載せず、下部の表に記載を行う</t>
         </is>
       </c>
-      <c r="F22" s="39" t="n"/>
-      <c r="G22" s="42" t="n"/>
-      <c r="H22" s="42" t="n"/>
-      <c r="I22" s="42" t="n"/>
-      <c r="J22" s="43" t="n"/>
-      <c r="K22" s="39" t="n"/>
-      <c r="L22" s="42" t="n"/>
-      <c r="M22" s="42" t="n"/>
-      <c r="N22" s="43" t="n"/>
+      <c r="F22" s="44" t="n"/>
+      <c r="G22" s="57" t="inlineStr">
+        <is>
+          <t>原子炉補機冷却水冷却器他について、解体撤去する。</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="n"/>
+      <c r="I22" s="40" t="n"/>
+      <c r="J22" s="44" t="n"/>
+      <c r="K22" s="35" t="inlineStr">
+        <is>
+          <t>原子炉補機冷却水冷却器他について、解体撤去する。</t>
+        </is>
+      </c>
+      <c r="L22" s="40" t="n"/>
+      <c r="M22" s="40" t="n"/>
+      <c r="N22" s="44" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="56" t="inlineStr">
         <is>
           <t>実施理由
 ※実績時：計画と実績の差異内容及びその理由</t>
         </is>
       </c>
-      <c r="F23" s="39" t="n"/>
-      <c r="G23" s="42" t="n"/>
-      <c r="H23" s="42" t="n"/>
-      <c r="I23" s="42" t="n"/>
-      <c r="J23" s="43" t="n"/>
-      <c r="K23" s="39" t="n"/>
-      <c r="L23" s="42" t="n"/>
-      <c r="M23" s="42" t="n"/>
-      <c r="N23" s="43" t="n"/>
+      <c r="F23" s="44" t="n"/>
+      <c r="G23" s="57" t="inlineStr">
+        <is>
+          <t>○○のため廃棄物処理を進める必要があり、○○系統解体後のスペースを廃棄物処理エリアとして活用するため。</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="n"/>
+      <c r="I23" s="40" t="n"/>
+      <c r="J23" s="44" t="n"/>
+      <c r="K23" s="35" t="inlineStr">
+        <is>
+          <t>○○のため廃棄物処理を進める必要があり、○○系統解体後のスペースを廃棄物処理エリアとして活用するため。</t>
+        </is>
+      </c>
+      <c r="L23" s="40" t="n"/>
+      <c r="M23" s="40" t="n"/>
+      <c r="N23" s="44" t="n"/>
     </row>
     <row r="24" ht="60" customHeight="1">
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="58" t="inlineStr">
         <is>
           <t>実施費用低減策</t>
         </is>
       </c>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="42" t="n"/>
-      <c r="H24" s="42" t="n"/>
-      <c r="I24" s="42" t="n"/>
-      <c r="J24" s="43" t="n"/>
-      <c r="K24" s="54" t="n"/>
-      <c r="L24" s="42" t="n"/>
-      <c r="M24" s="42" t="n"/>
-      <c r="N24" s="43" t="n"/>
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="59" t="inlineStr">
+        <is>
+          <t>○○工事と装置を共用することで費用低減を図った。</t>
+        </is>
+      </c>
+      <c r="H24" s="40" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="44" t="n"/>
+      <c r="K24" s="27" t="inlineStr">
+        <is>
+          <t>○○工事と装置を共用することで費用低減を図った。</t>
+        </is>
+      </c>
+      <c r="L24" s="40" t="n"/>
+      <c r="M24" s="40" t="n"/>
+      <c r="N24" s="44" t="n"/>
     </row>
     <row r="25" ht="60" customHeight="1">
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="58" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="42" t="n"/>
-      <c r="H25" s="42" t="n"/>
-      <c r="I25" s="42" t="n"/>
-      <c r="J25" s="43" t="n"/>
-      <c r="K25" s="54" t="n"/>
-      <c r="L25" s="42" t="n"/>
-      <c r="M25" s="42" t="n"/>
-      <c r="N25" s="43" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="59" t="inlineStr">
+        <is>
+          <t>複数号炉の実施件名の場合は号炉の按分の考え方を説明</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="44" t="n"/>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>複数号炉の実施件名の場合は号炉の按分の考え方を説明</t>
+        </is>
+      </c>
+      <c r="L25" s="40" t="n"/>
+      <c r="M25" s="40" t="n"/>
+      <c r="N25" s="44" t="n"/>
     </row>
     <row r="26" ht="13.2" customHeight="1">
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>実施内容（解体機器・解体物量）</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="F26" s="42" t="n"/>
-      <c r="G26" s="42" t="n"/>
-      <c r="H26" s="42" t="n"/>
-      <c r="I26" s="42" t="n"/>
-      <c r="J26" s="42" t="n"/>
-      <c r="K26" s="42" t="n"/>
-      <c r="L26" s="42" t="n"/>
-      <c r="M26" s="42" t="n"/>
-      <c r="N26" s="43" t="n"/>
+      <c r="C26" s="40" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="40" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="40" t="n"/>
+      <c r="K26" s="40" t="n"/>
+      <c r="L26" s="40" t="n"/>
+      <c r="M26" s="40" t="n"/>
+      <c r="N26" s="44" t="n"/>
     </row>
     <row r="27" ht="19.95" customHeight="1">
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>対象年度</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>▼分類</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>解体機器</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>作業区域
 （非管理区域・管理区域・埋区域）</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>支払い対象可否</t>
         </is>
       </c>
-      <c r="G27" s="25" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>計画</t>
         </is>
       </c>
-      <c r="H27" s="42" t="n"/>
-      <c r="I27" s="42" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="H27" s="40" t="n"/>
+      <c r="I27" s="40" t="n"/>
+      <c r="J27" s="44" t="n"/>
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="L27" s="42" t="n"/>
-      <c r="M27" s="42" t="n"/>
-      <c r="N27" s="43" t="n"/>
+      <c r="L27" s="40" t="n"/>
+      <c r="M27" s="40" t="n"/>
+      <c r="N27" s="44" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="56" t="n"/>
-      <c r="C28" s="56" t="n"/>
-      <c r="D28" s="56" t="n"/>
-      <c r="E28" s="56" t="n"/>
-      <c r="F28" s="56" t="n"/>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="B28" s="62" t="n"/>
+      <c r="C28" s="62" t="n"/>
+      <c r="D28" s="62" t="n"/>
+      <c r="E28" s="62" t="n"/>
+      <c r="F28" s="62" t="n"/>
+      <c r="G28" s="31" t="inlineStr">
         <is>
           <t>員数
 （台数）</t>
         </is>
       </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="31" t="inlineStr">
         <is>
           <t>解体物量
 （t）</t>
         </is>
       </c>
-      <c r="I28" s="25" t="inlineStr">
+      <c r="I28" s="31" t="inlineStr">
         <is>
           <t>工数
 （人・時間）</t>
         </is>
       </c>
-      <c r="J28" s="25" t="inlineStr">
+      <c r="J28" s="31" t="inlineStr">
         <is>
           <t>費用</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>員数
 （台数）</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>解体物量
 （t）</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>工数
 （人・時間）</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="N28" s="6" t="inlineStr">
         <is>
           <t>費用</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="57" t="inlineStr">
+      <c r="B29" s="63" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C29" s="42" t="n"/>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
-      <c r="F29" s="43" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="16" t="n">
+      <c r="C29" s="40" t="n"/>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="16" t="n">
+      <c r="I29" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="19" t="n"/>
-      <c r="L29" s="17" t="n">
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="17" t="n">
+      <c r="M29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="17" t="n">
+      <c r="N29" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>ポンプ・モータ</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Bポンプ</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>非管理区域</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>支払い対象</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N30" s="12" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="n"/>
-      <c r="M31" s="15" t="n"/>
-      <c r="N31" s="15" t="n"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>タンク・脱塩塔</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>○○タンク（屋外）</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>管理区域</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>支払い対象外</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="15" t="n"/>
-      <c r="L33" s="15" t="n"/>
-      <c r="M33" s="15" t="n"/>
-      <c r="N33" s="15" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="15" t="n"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="14" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="14" t="n"/>
-      <c r="K35" s="15" t="n"/>
-      <c r="L35" s="15" t="n"/>
-      <c r="M35" s="15" t="n"/>
-      <c r="N35" s="15" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="12" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="14" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="14" t="n"/>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
-      <c r="M37" s="15" t="n"/>
-      <c r="N37" s="15" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="58">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="K23:N23"/>
     <mergeCell ref="B27:B28"/>
-    <mergeCell ref="K23:N23"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="K17:N17"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="K10:N10"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="K19:N19"/>
-    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="K6:N6"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F21:J21"/>
     <mergeCell ref="K13:N13"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="F24:J24"/>
     <mergeCell ref="K18:N18"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="F20:J20"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="K25:N25"/>
-    <mergeCell ref="F5:J5"/>
     <mergeCell ref="K16:N16"/>
-    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="K24:N24"/>
     <mergeCell ref="K15:N15"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F8:J8"/>
     <mergeCell ref="K5:N5"/>
-    <mergeCell ref="F17:J17"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="K21:N21"/>
-    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C27:C28"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="K20:N20"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F9:J9"/>
     <mergeCell ref="K22:N22"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="K12:N12"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="E18:F18"/>
     <mergeCell ref="K27:N27"/>
-    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
